--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-09-04</t>
+          <t>2026-07-23 ~ 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6,351건</t>
+          <t>6,572건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1,188건</t>
+          <t>1,228건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2334</t>
+          <t>0.2331</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.0%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.5% ~ +0.8%</t>
+          <t>-4.6% ~ +0.7%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.6%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-10.1% ~ -4.8%</t>
+          <t>-10.2% ~ -4.9%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>951</v>
+        <v>982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,12 +725,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1770</v>
+        <v>1837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="4">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1485</v>
+        <v>1533</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1207</v>
+        <v>1247</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2135</v>
+        <v>2210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -949,27 +949,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>-0.4%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1457</v>
+        <v>1507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1430</v>
+        <v>1480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1329</v>
+        <v>1375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4134</v>
+        <v>4267</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2322</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2003</v>
+        <v>2091</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2357</v>
+        <v>0.2353</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="확률구간별" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="마켓별" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="리그별" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확률구간별" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="마켓별" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="리그별" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
